--- a/public/exports/29189625.xlsx
+++ b/public/exports/29189625.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258043</t>
+          <t xml:space="preserve">311258047</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286988</t>
+          <t xml:space="preserve">311286996</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286960</t>
+          <t xml:space="preserve">311286964</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">

--- a/public/exports/29189625.xlsx
+++ b/public/exports/29189625.xlsx
@@ -9214,7 +9214,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265936</t>
+          <t xml:space="preserve">311265937</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286963</t>
+          <t xml:space="preserve">311286967</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286990</t>
+          <t xml:space="preserve">311287000</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">

--- a/public/exports/29189625.xlsx
+++ b/public/exports/29189625.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258047</t>
+          <t xml:space="preserve">311258043</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265937</t>
+          <t xml:space="preserve">311265936</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286967</t>
+          <t xml:space="preserve">311286963</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286996</t>
+          <t xml:space="preserve">311286988</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286964</t>
+          <t xml:space="preserve">311286960</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287000</t>
+          <t xml:space="preserve">311286990</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
